--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6197-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6197-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39AE7AD1-3A73-42A9-B2EF-6901ED1774F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20F45446-31CE-4F1C-A0B1-6FA23CC93590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{948ABFD0-FD6E-4598-8A09-456977C9AEF7}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{5E50A50C-E994-40F5-83FB-732E8BF67AB9}"/>
   </bookViews>
   <sheets>
     <sheet name="6197-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1472,21 +1472,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E04ADAF-8353-4C5E-805F-FF8A99016363}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31276D60-83E4-407B-8F01-EDF4D25B3C5C}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1514,7 +1514,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1544,7 +1544,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1640,7 +1640,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>2024</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>25</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>25</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2023</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>25</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="39">
         <v>2022</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>25</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>25</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2021</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>25</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>25</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2019</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2018</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2017</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2016</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2015</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2014</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2013</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2012</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2011</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2010</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2009</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2008</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2007</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2006</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2005</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2004</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2003</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2002</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2001</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39" t="s">
         <v>43</v>
       </c>
